--- a/registrations.xlsx
+++ b/registrations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -873,9 +873,41 @@
         <v>cat</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>DIYA SINGLA</v>
+      </c>
+      <c r="B16" t="str">
+        <v>pranjalsingla0001@gmail.com</v>
+      </c>
+      <c r="C16" t="str">
+        <v>9354543672</v>
+      </c>
+      <c r="D16" t="str">
+        <v>21</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Real-Time Workouts</v>
+      </c>
+      <c r="G16" t="str">
+        <v>62</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Weight Loss</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Live Classes</v>
+      </c>
+      <c r="J16" t="str">
+        <v>pranjal</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
   </ignoredErrors>
 </worksheet>
 </file>